--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20232.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>KEVYN DANIEL</t>
   </si>
 </sst>
 </file>
@@ -646,16 +655,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>56.67</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -669,16 +681,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>82.76000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -692,16 +707,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>82.61</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -715,16 +733,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>57.58</v>
+      </c>
+      <c r="H5">
+        <v>6.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -738,16 +759,19 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="H6">
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -803,13 +827,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>56.67</v>
       </c>
       <c r="H2">
         <v>6.6</v>
@@ -864,7 +888,7 @@
         <v>82.61</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -890,7 +914,7 @@
         <v>57.58</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -907,16 +931,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -926,7 +950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -956,6 +980,29 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920192</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20232.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,15 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>KEVYN DANIEL</t>
   </si>
 </sst>
 </file>
@@ -827,16 +818,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>56.67</v>
+        <v>80</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -853,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>82.76000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -879,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>82.61</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H4">
         <v>7.7</v>
@@ -905,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>57.58</v>
+        <v>93.94</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -931,16 +922,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -950,7 +941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -980,29 +971,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920192</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20232.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
   </si>
 </sst>
 </file>
@@ -941,7 +950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -971,6 +980,29 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920189</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
